--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692AA98F-E30A-410B-8EC0-6E8A4A576ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1DDD9D-049F-492D-8C9E-9909FD3E3A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14108" uniqueCount="4547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14122" uniqueCount="4571">
   <si>
     <t>大正新脩大藏經</t>
   </si>
@@ -13910,8 +13910,98 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>T09n0262_p0056c02 T0262 (卷7) 妙法蓮華經觀世音菩薩普門品</t>
+    <t>譯述篇</t>
+  </si>
+  <si>
+    <t>YP0030 大乘佛教思想論</t>
+  </si>
+  <si>
+    <t>YP0032 天臺性具思想論</t>
+  </si>
+  <si>
+    <t>YP0033 瑜伽師地論解題</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0034 攝大乘論解題</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0035 阿利安文化與佛教的成立</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0036 中論相關性的論理</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>雜說篇</t>
+  </si>
+  <si>
+    <t>YP0037 三寶歌解說</t>
+  </si>
+  <si>
+    <t>YP0038 佛教的緣起觀</t>
+  </si>
+  <si>
+    <t>YP0039 印度部派佛教思想觀</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0040 人間佛陀</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0041 識法相及其思想演變</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0042 業及依業而有的輪迴</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JA088 (=T46n1915_p0473b11) 始終心要</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T46n1915_p0473b11 T1915 (卷1) 修習止觀坐禪法要〈始終心要〉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T46n1937_p0868a23 T1937 (卷2) 四明尊者教行錄〈修懺要旨〉</t>
     <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>T16n0663_p0340a07 T0663 (卷1) 金光明經〈空品〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>T24n1488_p1047a25 T1488 (卷3) 優婆塞戒經〈受戒品〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>X61n1164_p0745b07 X1164 (卷9) 淨土十要〈幽溪無盡法師淨土法語〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB144 (=X1342+X68n1315_p0272b20) 雲菴真淨禪師語錄</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X68n1315_p0272b20 X1315 (卷42) 古尊宿語錄〈寶峰雲庵真淨禪師住筠州聖壽語錄〉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X60n1123_p0540a16 X1123 (卷3) 在家律要廣集〈梵網經懺悔行法〉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T09n0262_p0056c02 T0262 (卷7) 妙法蓮華經〈妙法蓮華經觀世音菩薩普門品〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB214 (=X0615+T1939+X0974+X1137+X60n1123_p0540a16+X1124+X0703+T1500+選錄) 蕅益大師佛學十種</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14901,8 +14991,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C640C8-AF4E-454A-93BC-513EE82F584A}">
-  <dimension ref="A1:F4700"/>
+  <dimension ref="A1:F4714"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -26301,7 +26395,7 @@
     </row>
     <row r="2280" spans="2:5">
       <c r="E2280" t="s">
-        <v>4546</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="2281" spans="2:5">
@@ -27161,12 +27255,12 @@
     </row>
     <row r="2452" spans="4:5">
       <c r="D2452" t="s">
-        <v>2404</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="2453" spans="4:5">
       <c r="E2453" t="s">
-        <v>2405</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="2454" spans="4:5">
@@ -27176,7 +27270,7 @@
     </row>
     <row r="2455" spans="4:5">
       <c r="E2455" t="s">
-        <v>2407</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="2456" spans="4:5">
@@ -28631,7 +28725,7 @@
     </row>
     <row r="2746" spans="4:5">
       <c r="E2746" t="s">
-        <v>2696</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="2747" spans="4:5">
@@ -28666,7 +28760,7 @@
     </row>
     <row r="2753" spans="4:5">
       <c r="E2753" t="s">
-        <v>2703</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="2754" spans="4:5">
@@ -28971,7 +29065,7 @@
     </row>
     <row r="2814" spans="4:5">
       <c r="E2814" t="s">
-        <v>2762</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="2815" spans="4:5">
@@ -29551,7 +29645,7 @@
     </row>
     <row r="2930" spans="4:5">
       <c r="D2930" t="s">
-        <v>2876</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="2931" spans="4:5">
@@ -29561,7 +29655,7 @@
     </row>
     <row r="2932" spans="4:5">
       <c r="E2932" t="s">
-        <v>2878</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="2933" spans="4:5">
@@ -30036,7 +30130,7 @@
     </row>
     <row r="3027" spans="4:5">
       <c r="D3027" t="s">
-        <v>2973</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="3028" spans="4:5">
@@ -30061,7 +30155,7 @@
     </row>
     <row r="3032" spans="4:5">
       <c r="E3032" t="s">
-        <v>2978</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="3033" spans="4:5">
@@ -38435,66 +38529,171 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="4689" spans="2:4" s="1" customFormat="1">
+    <row r="4689" spans="1:6" s="1" customFormat="1">
       <c r="D4689" s="1" t="s">
         <v>4501</v>
       </c>
     </row>
-    <row r="4690" spans="2:4" s="1" customFormat="1">
+    <row r="4690" spans="1:6" s="1" customFormat="1">
       <c r="D4690" s="1" t="s">
         <v>4502</v>
       </c>
     </row>
-    <row r="4691" spans="2:4" s="1" customFormat="1">
+    <row r="4691" spans="1:6" s="1" customFormat="1">
       <c r="D4691" s="1" t="s">
         <v>4531</v>
       </c>
     </row>
-    <row r="4692" spans="2:4" s="1" customFormat="1">
+    <row r="4692" spans="1:6" s="1" customFormat="1">
       <c r="D4692" s="3" t="s">
         <v>4532</v>
       </c>
     </row>
-    <row r="4693" spans="2:4" s="1" customFormat="1">
+    <row r="4693" spans="1:6" s="1" customFormat="1">
       <c r="D4693" t="s">
         <v>4533</v>
       </c>
     </row>
-    <row r="4694" spans="2:4">
-      <c r="B4694" t="s">
+    <row r="4694" spans="1:6" s="1" customFormat="1">
+      <c r="C4694" s="3" t="s">
+        <v>4546</v>
+      </c>
+      <c r="D4694" s="3"/>
+    </row>
+    <row r="4695" spans="1:6" s="1" customFormat="1">
+      <c r="C4695" s="3"/>
+      <c r="D4695" s="3" t="s">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="4696" spans="1:6" s="1" customFormat="1">
+      <c r="C4696" s="3"/>
+      <c r="D4696" s="3" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="4697" spans="1:6" s="1" customFormat="1">
+      <c r="C4697" s="3"/>
+      <c r="D4697" t="s">
+        <v>4549</v>
+      </c>
+    </row>
+    <row r="4698" spans="1:6" s="1" customFormat="1">
+      <c r="C4698" s="3"/>
+      <c r="D4698" t="s">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="4699" spans="1:6" s="1" customFormat="1">
+      <c r="C4699" s="3"/>
+      <c r="D4699" t="s">
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="4700" spans="1:6" s="1" customFormat="1">
+      <c r="C4700" s="3"/>
+      <c r="D4700" t="s">
+        <v>4552</v>
+      </c>
+    </row>
+    <row r="4701" spans="1:6">
+      <c r="A4701" s="1"/>
+      <c r="B4701" s="1"/>
+      <c r="C4701" t="s">
+        <v>4553</v>
+      </c>
+      <c r="E4701" s="1"/>
+      <c r="F4701" s="1"/>
+    </row>
+    <row r="4702" spans="1:6">
+      <c r="A4702" s="1"/>
+      <c r="B4702" s="1"/>
+      <c r="D4702" t="s">
+        <v>4554</v>
+      </c>
+      <c r="E4702" s="1"/>
+      <c r="F4702" s="1"/>
+    </row>
+    <row r="4703" spans="1:6">
+      <c r="A4703" s="1"/>
+      <c r="B4703" s="1"/>
+      <c r="D4703" t="s">
+        <v>4555</v>
+      </c>
+      <c r="E4703" s="1"/>
+      <c r="F4703" s="1"/>
+    </row>
+    <row r="4704" spans="1:6">
+      <c r="A4704" s="1"/>
+      <c r="B4704" s="1"/>
+      <c r="D4704" t="s">
+        <v>4556</v>
+      </c>
+      <c r="E4704" s="1"/>
+      <c r="F4704" s="1"/>
+    </row>
+    <row r="4705" spans="1:6">
+      <c r="A4705" s="1"/>
+      <c r="B4705" s="1"/>
+      <c r="D4705" t="s">
+        <v>4557</v>
+      </c>
+      <c r="E4705" s="1"/>
+      <c r="F4705" s="1"/>
+    </row>
+    <row r="4706" spans="1:6">
+      <c r="A4706" s="1"/>
+      <c r="B4706" s="1"/>
+      <c r="D4706" t="s">
+        <v>4558</v>
+      </c>
+      <c r="E4706" s="1"/>
+      <c r="F4706" s="1"/>
+    </row>
+    <row r="4707" spans="1:6">
+      <c r="A4707" s="1"/>
+      <c r="B4707" s="1"/>
+      <c r="D4707" t="s">
+        <v>4559</v>
+      </c>
+      <c r="E4707" s="1"/>
+      <c r="F4707" s="1"/>
+    </row>
+    <row r="4708" spans="1:6">
+      <c r="B4708" t="s">
         <v>4435</v>
       </c>
     </row>
-    <row r="4695" spans="2:4">
-      <c r="C4695" s="1" t="s">
+    <row r="4709" spans="1:6">
+      <c r="C4709" s="1" t="s">
         <v>4436</v>
       </c>
     </row>
-    <row r="4696" spans="2:4">
-      <c r="C4696" s="1" t="s">
+    <row r="4710" spans="1:6">
+      <c r="C4710" s="1" t="s">
         <v>4440</v>
       </c>
     </row>
-    <row r="4697" spans="2:4">
-      <c r="B4697" s="1"/>
-      <c r="C4697" s="1" t="s">
+    <row r="4711" spans="1:6">
+      <c r="B4711" s="1"/>
+      <c r="C4711" s="1" t="s">
         <v>4444</v>
       </c>
     </row>
-    <row r="4698" spans="2:4">
-      <c r="B4698" s="1"/>
-      <c r="C4698" s="1" t="s">
+    <row r="4712" spans="1:6">
+      <c r="B4712" s="1"/>
+      <c r="C4712" s="1" t="s">
         <v>4445</v>
       </c>
     </row>
-    <row r="4699" spans="2:4">
-      <c r="B4699" s="1"/>
-      <c r="C4699" s="1" t="s">
+    <row r="4713" spans="1:6">
+      <c r="B4713" s="1"/>
+      <c r="C4713" s="1" t="s">
         <v>4446</v>
       </c>
     </row>
-    <row r="4700" spans="2:4">
-      <c r="C4700" s="1" t="s">
+    <row r="4714" spans="1:6">
+      <c r="C4714" s="1" t="s">
         <v>4448</v>
       </c>
     </row>

--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1DDD9D-049F-492D-8C9E-9909FD3E3A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966413B2-06FF-4AD6-BA01-62C8B4B7654C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13870,46 +13870,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>JB277_019..021 JB277 (卷19-21) 雲棲法彙（選錄）雲棲大師遺稿</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_025 JB277 (卷25) 雲棲法彙（選錄）雲棲大師塔銘</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_023 JB277 (卷23) 雲棲法彙（選錄）雲棲紀事</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_012 JB277 (卷12) 雲棲法彙（選錄）竹窗隨筆</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_013 JB277 (卷13) 雲棲法彙（選錄）竹窗二筆</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_014 JB277 (卷14) 雲棲法彙（選錄）竹窗三筆</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_015 JB277 (卷15) 雲棲法彙（選錄）正訛集</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_022 JB277 (卷22) 雲棲法彙（選錄）雲棲共住規約</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_016 JB277 (卷16) 雲棲法彙（選錄）直道錄</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>JB277_017..018 JB277 (卷17-18) 雲棲法彙（選錄）山房雜錄</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>譯述篇</t>
   </si>
   <si>
@@ -13964,44 +13924,84 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>T46n1915_p0473b11 T1915 (卷1) 修習止觀坐禪法要〈始終心要〉</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>T46n1937_p0868a23 T1937 (卷2) 四明尊者教行錄〈修懺要旨〉</t>
-    <phoneticPr fontId="23" type="noConversion"/>
-  </si>
-  <si>
-    <t>T16n0663_p0340a07 T0663 (卷1) 金光明經〈空品〉</t>
-    <phoneticPr fontId="23" type="noConversion"/>
-  </si>
-  <si>
-    <t>T24n1488_p1047a25 T1488 (卷3) 優婆塞戒經〈受戒品〉</t>
-    <phoneticPr fontId="23" type="noConversion"/>
-  </si>
-  <si>
-    <t>X61n1164_p0745b07 X1164 (卷9) 淨土十要〈幽溪無盡法師淨土法語〉</t>
-    <phoneticPr fontId="23" type="noConversion"/>
-  </si>
-  <si>
     <t>JB144 (=X1342+X68n1315_p0272b20) 雲菴真淨禪師語錄</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>X68n1315_p0272b20 X1315 (卷42) 古尊宿語錄〈寶峰雲庵真淨禪師住筠州聖壽語錄〉</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>X60n1123_p0540a16 X1123 (卷3) 在家律要廣集〈梵網經懺悔行法〉</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>T09n0262_p0056c02 T0262 (卷7) 妙法蓮華經〈妙法蓮華經觀世音菩薩普門品〉</t>
-    <phoneticPr fontId="23" type="noConversion"/>
-  </si>
-  <si>
     <t>JB214 (=X0615+T1939+X0974+X1137+X60n1123_p0540a16+X1124+X0703+T1500+選錄) 蕅益大師佛學十種</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T09n0262_p0056c02 T0262 妙法蓮華經 (卷7) 〈妙法蓮華經觀世音菩薩普門品〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>T46n1915_p0473b11 T1915 修習止觀坐禪法要 (卷1) 〈始終心要〉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>T46n1937_p0868a23 T1937 四明尊者教行錄 (卷2) 〈修懺要旨〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>T16n0663_p0340a07 T0663 金光明經 (卷1) 〈空品〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>T24n1488_p1047a25 T1488 優婆塞戒經 (卷3) 〈受戒品〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>X61n1164_p0745b07 X1164 淨土十要 (卷9) 〈幽溪無盡法師淨土法語〉</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>X68n1315_p0272b20 X1315 古尊宿語錄 (卷42) 〈寶峰雲庵真淨禪師住筠州聖壽語錄〉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X60n1123_p0540a16 X1123 在家律要廣集 (卷3) 〈梵網經懺悔行法〉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_019..021 JB277 雲棲法彙（選錄） (卷19-21) 〈雲棲大師遺稿〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_025 JB277 雲棲法彙（選錄） (卷25) 〈雲棲大師塔銘〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_023 JB277 雲棲法彙（選錄） (卷23) 〈雲棲紀事〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_012 JB277 雲棲法彙（選錄） (卷12) 〈竹窗隨筆〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_013 JB277 雲棲法彙（選錄） (卷13) 〈竹窗二筆〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_014 JB277 雲棲法彙（選錄） (卷14) 〈竹窗三筆〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_015 JB277 雲棲法彙（選錄） (卷15) 〈正訛集〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_022 JB277 雲棲法彙（選錄） (卷22) 〈雲棲共住規約〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_016 JB277 雲棲法彙（選錄） (卷16) 〈直道錄〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_017..018 JB277 雲棲法彙（選錄） (卷17-18) 〈山房雜錄〉</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -26395,7 +26395,7 @@
     </row>
     <row r="2280" spans="2:5">
       <c r="E2280" t="s">
-        <v>4569</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="2281" spans="2:5">
@@ -27255,12 +27255,12 @@
     </row>
     <row r="2452" spans="4:5">
       <c r="D2452" t="s">
-        <v>4560</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="2453" spans="4:5">
       <c r="E2453" t="s">
-        <v>4561</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="2454" spans="4:5">
@@ -27270,7 +27270,7 @@
     </row>
     <row r="2455" spans="4:5">
       <c r="E2455" t="s">
-        <v>4562</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="2456" spans="4:5">
@@ -28725,7 +28725,7 @@
     </row>
     <row r="2746" spans="4:5">
       <c r="E2746" t="s">
-        <v>4563</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="2747" spans="4:5">
@@ -28760,7 +28760,7 @@
     </row>
     <row r="2753" spans="4:5">
       <c r="E2753" t="s">
-        <v>4564</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="2754" spans="4:5">
@@ -29065,7 +29065,7 @@
     </row>
     <row r="2814" spans="4:5">
       <c r="E2814" t="s">
-        <v>4565</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="2815" spans="4:5">
@@ -29645,7 +29645,7 @@
     </row>
     <row r="2930" spans="4:5">
       <c r="D2930" t="s">
-        <v>4566</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="2931" spans="4:5">
@@ -29655,7 +29655,7 @@
     </row>
     <row r="2932" spans="4:5">
       <c r="E2932" t="s">
-        <v>4567</v>
+        <v>4559</v>
       </c>
     </row>
     <row r="2933" spans="4:5">
@@ -30130,7 +30130,7 @@
     </row>
     <row r="3027" spans="4:5">
       <c r="D3027" t="s">
-        <v>4570</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="3028" spans="4:5">
@@ -30155,7 +30155,7 @@
     </row>
     <row r="3032" spans="4:5">
       <c r="E3032" t="s">
-        <v>4568</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="3033" spans="4:5">
@@ -37290,27 +37290,29 @@
     </row>
     <row r="4449" spans="4:5">
       <c r="E4449" t="s">
-        <v>4536</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="4450" spans="4:5">
       <c r="D4450" t="s">
         <v>4000</v>
       </c>
+      <c r="E4450" s="1"/>
     </row>
     <row r="4451" spans="4:5">
       <c r="E4451" t="s">
-        <v>4537</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="4452" spans="4:5">
       <c r="D4452" t="s">
         <v>4002</v>
       </c>
+      <c r="E4452" s="1"/>
     </row>
     <row r="4453" spans="4:5">
       <c r="E4453" t="s">
-        <v>4538</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="4454" spans="4:5">
@@ -37320,7 +37322,7 @@
     </row>
     <row r="4455" spans="4:5">
       <c r="E4455" t="s">
-        <v>4539</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="4456" spans="4:5">
@@ -37330,7 +37332,7 @@
     </row>
     <row r="4457" spans="4:5">
       <c r="E4457" t="s">
-        <v>4540</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="4458" spans="4:5">
@@ -37340,7 +37342,7 @@
     </row>
     <row r="4459" spans="4:5">
       <c r="E4459" t="s">
-        <v>4541</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="4460" spans="4:5">
@@ -37350,7 +37352,7 @@
     </row>
     <row r="4461" spans="4:5">
       <c r="E4461" t="s">
-        <v>4542</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="4462" spans="4:5">
@@ -37360,7 +37362,7 @@
     </row>
     <row r="4463" spans="4:5">
       <c r="E4463" t="s">
-        <v>4543</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="4464" spans="4:5">
@@ -37370,7 +37372,7 @@
     </row>
     <row r="4465" spans="3:5">
       <c r="E4465" t="s">
-        <v>4544</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="4466" spans="3:5">
@@ -37380,7 +37382,7 @@
     </row>
     <row r="4467" spans="3:5">
       <c r="E4467" t="s">
-        <v>4545</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="4468" spans="3:5">
@@ -38556,51 +38558,51 @@
     </row>
     <row r="4694" spans="1:6" s="1" customFormat="1">
       <c r="C4694" s="3" t="s">
-        <v>4546</v>
+        <v>4536</v>
       </c>
       <c r="D4694" s="3"/>
     </row>
     <row r="4695" spans="1:6" s="1" customFormat="1">
       <c r="C4695" s="3"/>
       <c r="D4695" s="3" t="s">
-        <v>4547</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="4696" spans="1:6" s="1" customFormat="1">
       <c r="C4696" s="3"/>
       <c r="D4696" s="3" t="s">
-        <v>4548</v>
+        <v>4538</v>
       </c>
     </row>
     <row r="4697" spans="1:6" s="1" customFormat="1">
       <c r="C4697" s="3"/>
       <c r="D4697" t="s">
-        <v>4549</v>
+        <v>4539</v>
       </c>
     </row>
     <row r="4698" spans="1:6" s="1" customFormat="1">
       <c r="C4698" s="3"/>
       <c r="D4698" t="s">
-        <v>4550</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="4699" spans="1:6" s="1" customFormat="1">
       <c r="C4699" s="3"/>
       <c r="D4699" t="s">
-        <v>4551</v>
+        <v>4541</v>
       </c>
     </row>
     <row r="4700" spans="1:6" s="1" customFormat="1">
       <c r="C4700" s="3"/>
       <c r="D4700" t="s">
-        <v>4552</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="4701" spans="1:6">
       <c r="A4701" s="1"/>
       <c r="B4701" s="1"/>
       <c r="C4701" t="s">
-        <v>4553</v>
+        <v>4543</v>
       </c>
       <c r="E4701" s="1"/>
       <c r="F4701" s="1"/>
@@ -38609,7 +38611,7 @@
       <c r="A4702" s="1"/>
       <c r="B4702" s="1"/>
       <c r="D4702" t="s">
-        <v>4554</v>
+        <v>4544</v>
       </c>
       <c r="E4702" s="1"/>
       <c r="F4702" s="1"/>
@@ -38618,7 +38620,7 @@
       <c r="A4703" s="1"/>
       <c r="B4703" s="1"/>
       <c r="D4703" t="s">
-        <v>4555</v>
+        <v>4545</v>
       </c>
       <c r="E4703" s="1"/>
       <c r="F4703" s="1"/>
@@ -38627,7 +38629,7 @@
       <c r="A4704" s="1"/>
       <c r="B4704" s="1"/>
       <c r="D4704" t="s">
-        <v>4556</v>
+        <v>4546</v>
       </c>
       <c r="E4704" s="1"/>
       <c r="F4704" s="1"/>
@@ -38636,7 +38638,7 @@
       <c r="A4705" s="1"/>
       <c r="B4705" s="1"/>
       <c r="D4705" t="s">
-        <v>4557</v>
+        <v>4547</v>
       </c>
       <c r="E4705" s="1"/>
       <c r="F4705" s="1"/>
@@ -38645,7 +38647,7 @@
       <c r="A4706" s="1"/>
       <c r="B4706" s="1"/>
       <c r="D4706" t="s">
-        <v>4558</v>
+        <v>4548</v>
       </c>
       <c r="E4706" s="1"/>
       <c r="F4706" s="1"/>
@@ -38654,7 +38656,7 @@
       <c r="A4707" s="1"/>
       <c r="B4707" s="1"/>
       <c r="D4707" t="s">
-        <v>4559</v>
+        <v>4549</v>
       </c>
       <c r="E4707" s="1"/>
       <c r="F4707" s="1"/>
